--- a/hardis-report/xls/backup-updated-files-monitoring_orgfarm_01772716d5_dev_ed_develop.xlsx
+++ b/hardis-report/xls/backup-updated-files-monitoring_orgfarm_01772716d5_dev_ed_develop.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>File</t>
   </si>
@@ -50,75 +50,6 @@
   </si>
   <si>
     <t>📰</t>
-  </si>
-  <si>
-    <t>layouts/Installation__c-Installation Layout.layout-meta.xml</t>
-  </si>
-  <si>
-    <t>Layout Installation__c-Installation Layout</t>
-  </si>
-  <si>
-    <t>layouts/Panel_Batch__c-Panel Batch Layout.layout-meta.xml</t>
-  </si>
-  <si>
-    <t>Layout Panel_Batch__c-Panel Batch Layout</t>
-  </si>
-  <si>
-    <t>objects/Installation__c/fields/Gate_Code__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>CustomFieldTranslation Gate_Code__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>objects/Installation__c/fields/Install_Date__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>CustomFieldTranslation Install_Date__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>objects/Installation__c/fields/Scaffolding_Required__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>CustomFieldTranslation Scaffolding_Required__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>objects/Installation__c/fields/Status__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>CustomFieldTranslation Status__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>objects/Panel_Batch__c/fields/Supplier__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>CustomFieldTranslation Supplier__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>objects/Panel_Batch__c/fields/Warranty_Years__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>CustomFieldTranslation Warranty_Years__c.field-meta.xml</t>
-  </si>
-  <si>
-    <t>permissionsets/Helios_Delivery_Crew.permissionset-meta.xml</t>
-  </si>
-  <si>
-    <t>PermissionSet Helios_Delivery_Crew</t>
-  </si>
-  <si>
-    <t>permissionsets/Helios_Delivery_Manager.permissionset-meta.xml</t>
-  </si>
-  <si>
-    <t>PermissionSet Helios_Delivery_Manager</t>
-  </si>
-  <si>
-    <t>manifest/package-all-org-items.xml</t>
-  </si>
-  <si>
-    <t>manifest/package-backup-items.xml</t>
   </si>
 </sst>
 </file>
@@ -180,8 +111,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Table_sheet1_1" displayName="Table_sheet1_1" ref="A1:G14" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:G14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Table_sheet1_1" displayName="Table_sheet1_1" ref="A1:G2" totalsRowShown="1" headerRowCount="1">
+  <autoFilter ref="A1:G2">
     <filterColumn colId="0" hiddenButton="0"/>
     <filterColumn colId="1" hiddenButton="0"/>
     <filterColumn colId="2" hiddenButton="0"/>
@@ -525,12 +456,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="60" style="1" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="60" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
@@ -543,7 +474,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -566,7 +497,7 @@
       <c r="B2" s="2">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -579,282 +510,6 @@
         <v>11</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="2" t="s">
         <v>12</v>
       </c>
     </row>
